--- a/benchmarks/attachment_intelligence/fixtures/files/f10.xlsx
+++ b/benchmarks/attachment_intelligence/fixtures/files/f10.xlsx
@@ -52,7 +52,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Количество</t>
+          <t xml:space="preserve">Кол-во</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -62,12 +62,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цена за ед., руб.</t>
+          <t xml:space="preserve">Цена, руб.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стоимость, руб.</t>
+          <t xml:space="preserve">Стоимость</t>
         </is>
       </c>
     </row>
